--- a/engine/publish_queue/SWDY/SWDY_Valuation_Model_10092026_public.xlsx
+++ b/engine/publish_queue/SWDY/SWDY_Valuation_Model_10092026_public.xlsx
@@ -2561,19 +2561,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>103.9579534291615</v>
+        <v>104.0301624632969</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>116.5404104409828</v>
+        <v>116.6211865067517</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>134.9250535973918</v>
+        <v>135.0183472357894</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>164.5454667217586</v>
+        <v>164.6589280440988</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>220.698725084256</v>
+        <v>220.850419538668</v>
       </c>
     </row>
     <row r="7">
@@ -2583,19 +2583,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>87.6624525757782</v>
+        <v>87.72356300452299</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>95.7497920679405</v>
+        <v>95.81640862987639</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>106.800051725385</v>
+        <v>106.8741916763822</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>122.9278341935899</v>
+        <v>123.0129544822412</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>148.8880965042395</v>
+        <v>148.9908914140809</v>
       </c>
     </row>
     <row r="8">
@@ -2605,19 +2605,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>75.36259663302229</v>
+        <v>75.41532992422788</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>80.75351613072056</v>
+        <v>80.80991954166394</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>97.32517470782793</v>
+        <v>97.39286004781091</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>111.2606663334557</v>
+        <v>111.3378389089451</v>
       </c>
     </row>
     <row r="9">
@@ -2627,19 +2627,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>65.7551676969633</v>
+        <v>65.80135768206051</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>69.43185339144748</v>
+        <v>69.48054631668187</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>74.02908767939394</v>
+        <v>74.08091021732177</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>79.99204503129506</v>
+        <v>80.04792691139478</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>88.10811060392669</v>
+        <v>88.16951757590688</v>
       </c>
     </row>
     <row r="10">
@@ -2649,19 +2649,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>58.047869408913</v>
+        <v>58.08881027750758</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>60.58637439004508</v>
+        <v>60.62904327864683</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>63.65776038482486</v>
+        <v>63.70252003806494</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>67.48395285635333</v>
+        <v>67.53131708874184</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>72.42997389688901</v>
+        <v>72.48070500205404</v>
       </c>
     </row>
     <row r="12">
@@ -2706,19 +2706,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>142.9257201436457</v>
+        <v>143.024503881775</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>138.8532208372788</v>
+        <v>138.9492096007453</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>134.9250535973918</v>
+        <v>135.0183472357894</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>131.1348279469485</v>
+        <v>131.2255218523266</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>127.4764945640268</v>
+        <v>127.5646799108681</v>
       </c>
     </row>
     <row r="15">
@@ -2728,19 +2728,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>113.2043612990502</v>
+        <v>113.2828955946668</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>109.9445769200784</v>
+        <v>110.0208741777526</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>106.800051725385</v>
+        <v>106.8741916763822</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>103.7656914075321</v>
+        <v>103.8377502299199</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>100.8366732530279</v>
+        <v>100.9067237627105</v>
       </c>
     </row>
     <row r="16">
@@ -2750,19 +2750,19 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>93.08744362839961</v>
+        <v>93.15227219205939</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>90.37756045690212</v>
+        <v>90.44052949139993</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>85.24035794052051</v>
+        <v>85.29980334431518</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>82.80482756291119</v>
+        <v>82.86260313979236</v>
       </c>
     </row>
     <row r="17">
@@ -2772,19 +2772,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>78.57430312065637</v>
+        <v>78.62924392140498</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>76.26098688087828</v>
+        <v>76.31434039371382</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>74.02908767939394</v>
+        <v>74.08091021732177</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>71.87501939979802</v>
+        <v>71.92536477488245</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>69.79538660824731</v>
+        <v>69.84430626571906</v>
       </c>
     </row>
     <row r="18">
@@ -2794,19 +2794,19 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>67.61501378418899</v>
+        <v>67.66248813099821</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>65.60102680467182</v>
+        <v>65.64711934901671</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>63.65776038482486</v>
+        <v>63.70252003806494</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>61.78210484973862</v>
+        <v>61.82557835469562</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>59.97111565861656</v>
+        <v>60.01334770570721</v>
       </c>
     </row>
     <row r="20">
@@ -2841,19 +2841,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>92.11601318377691</v>
+        <v>92.17996995001533</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>90.6948601038554</v>
+        <v>90.75790998185289</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>88.2716081141819</v>
+        <v>88.33310907770868</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>87.76263937231083</v>
+        <v>87.82381459630682</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>87.25723444154944</v>
+        <v>87.31808606401808</v>
       </c>
       <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2867,19 +2867,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>87.76327116068845</v>
+        <v>87.82444678911779</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2893,19 +2893,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>50.91447338147828</v>
+        <v>50.950588067254</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>69.33887227108335</v>
+        <v>69.38751742818589</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>106.1876700502934</v>
+        <v>106.2613761500496</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>124.6120689398984</v>
+        <v>124.6983055109813</v>
       </c>
       <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2919,19 +2919,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>87.76327116068842</v>
+        <v>87.82444678911776</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>87.76327116068842</v>
+        <v>87.82444678911776</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>87.76327116068845</v>
+        <v>87.82444678911777</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2945,19 +2945,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>97.52765330261191</v>
+        <v>97.59544299620889</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>92.04204535771109</v>
+        <v>92.10611928435993</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>86.92214460913688</v>
+        <v>86.98275048663422</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>81.07082946790932</v>
+        <v>81.12747186066198</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>75.58522152300843</v>
+        <v>75.63814814881297</v>
       </c>
       <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -2971,19 +2971,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>66.47156186730963</v>
+        <v>66.51825425719441</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>83.04167945779123</v>
+        <v>83.09965272761718</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>99.51884490996628</v>
+        <v>99.58803577823238</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>108.5341680585322</v>
+        <v>108.6094965282676</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>116.1819146387544</v>
+        <v>116.2624496684627</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -2997,19 +2997,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>75.36259663302229</v>
+        <v>75.41532992422788</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>80.75351613072056</v>
+        <v>80.80991954166394</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>87.7632711606884</v>
+        <v>87.82444678911774</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>97.32517470782793</v>
+        <v>97.39286004781091</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>111.2606663334557</v>
+        <v>111.3378389089451</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -4016,14 +4016,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>28.78407997537623</v>
+        <v>28.80512018233149</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>133.7753850070414</v>
+        <v>133.8678939302773</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>28.78407997537623</v>
+        <v>28.80512018233149</v>
       </c>
     </row>
     <row r="7">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>133.7753850070414</v>
+        <v>133.8678939302773</v>
       </c>
     </row>
     <row r="8">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>81.67504702609115</v>
+        <v>81.73139139510033</v>
       </c>
     </row>
     <row r="19">
@@ -4614,13 +4614,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>173.7120513766789</v>
+        <v>173.8288364577823</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>127.4805164686761</v>
+        <v>127.5665686336996</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>219.9435862846818</v>
+        <v>220.0911042818651</v>
       </c>
     </row>
     <row r="24">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>93.77232461390484</v>
+        <v>93.83596889146507</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>33.87910174981675</v>
+        <v>33.90293135551509</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>64.15244367864858</v>
+        <v>64.19639781793219</v>
       </c>
     </row>
     <row r="25">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>89.33482995346847</v>
+        <v>89.39708757884019</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>66.64132982804048</v>
+        <v>66.68784309439387</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>81.67504702609115</v>
+        <v>81.73139139510033</v>
       </c>
     </row>
     <row r="26">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>2140.777876</v>
+        <v>2139.355716</v>
       </c>
     </row>
     <row r="7">
